--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.491526894192135</v>
+        <v>0.567373120306222</v>
       </c>
       <c r="D2" t="n">
-        <v>4.366963806080201</v>
+        <v>0.7096316184880327</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F2" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.36369291030804</v>
+        <v>2.496600097925056</v>
       </c>
       <c r="D3" t="n">
-        <v>15.39688645887933</v>
+        <v>2.501994049567891</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F3" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.07773877021457</v>
+        <v>3.912632550159868</v>
       </c>
       <c r="D4" t="n">
-        <v>24.05434468549365</v>
+        <v>3.908831011392718</v>
       </c>
       <c r="E4" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F4" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.47436081948667</v>
+        <v>6.414583633166584</v>
       </c>
       <c r="D5" t="n">
-        <v>39.44553437693322</v>
+        <v>6.409899336251649</v>
       </c>
       <c r="E5" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F5" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.18427332814733</v>
+        <v>1.979944415823941</v>
       </c>
       <c r="D6" t="n">
-        <v>9.448613434638593</v>
+        <v>1.535399683128772</v>
       </c>
       <c r="E6" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F6" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.89400759963537</v>
+        <v>6.320276234940748</v>
       </c>
       <c r="D7" t="n">
-        <v>34.14175552874662</v>
+        <v>5.548035273421326</v>
       </c>
       <c r="E7" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F7" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>26.81406025130275</v>
+        <v>4.357284790836697</v>
       </c>
       <c r="D8" t="n">
-        <v>19.09367396059183</v>
+        <v>3.102722018596172</v>
       </c>
       <c r="E8" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F8" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.46858401014737</v>
+        <v>5.113644901648948</v>
       </c>
       <c r="D9" t="n">
-        <v>31.45819656743211</v>
+        <v>5.111956942207717</v>
       </c>
       <c r="E9" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F9" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.8053174823848</v>
+        <v>6.468364090887531</v>
       </c>
       <c r="D10" t="n">
-        <v>39.43448531040691</v>
+        <v>6.408103862941123</v>
       </c>
       <c r="E10" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F10" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.87706615512556</v>
+        <v>4.367523250207904</v>
       </c>
       <c r="D11" t="n">
-        <v>27.44214823867449</v>
+        <v>4.459349088784604</v>
       </c>
       <c r="E11" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F11" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.12909753266605</v>
+        <v>6.358478349058234</v>
       </c>
       <c r="D12" t="n">
-        <v>39.66737110373513</v>
+        <v>6.445947804356958</v>
       </c>
       <c r="E12" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F12" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.80009873636874</v>
+        <v>5.16751604465992</v>
       </c>
       <c r="D13" t="n">
-        <v>32.41635348211459</v>
+        <v>5.267657440843622</v>
       </c>
       <c r="E13" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F13" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.28590733383989</v>
+        <v>7.196459941748982</v>
       </c>
       <c r="D14" t="n">
-        <v>44.92745811516167</v>
+        <v>7.300711943713772</v>
       </c>
       <c r="E14" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F14" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>39.13302375098178</v>
+        <v>6.35911635953454</v>
       </c>
       <c r="D15" t="n">
-        <v>39.52110374783737</v>
+        <v>6.422179359023573</v>
       </c>
       <c r="E15" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F15" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>44.17283428057649</v>
+        <v>7.178085570593679</v>
       </c>
       <c r="D16" t="n">
-        <v>44.85615697424191</v>
+        <v>7.289125508314311</v>
       </c>
       <c r="E16" t="n">
-        <v>11.9112658271763</v>
+        <v>1.93558069691615</v>
       </c>
       <c r="F16" t="n">
-        <v>12.33760043192664</v>
+        <v>2.004860070188079</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
